--- a/tools/undercity-crossref-matrix.xlsx
+++ b/tools/undercity-crossref-matrix.xlsx
@@ -973,7 +973,7 @@
     <t xml:space="preserve">Rail power flicker</t>
   </si>
   <si>
-    <t xml:space="preserve">Yard rail flickers on lamp-bank switching; match AGR West cycle code.</t>
+    <t xml:space="preserve">Yard rail flickers on lamp-bank switching; match AGR East cycle code.</t>
   </si>
   <si>
     <t xml:space="preserve">Grow-lamp bank failure</t>
@@ -1631,16 +1631,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1656,15 +1660,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1672,15 +1676,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1696,15 +1700,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1716,15 +1720,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1732,11 +1736,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1748,15 +1752,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1768,15 +1772,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1788,39 +1792,39 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2184,116 +2188,116 @@
   <dimension ref="B2:B25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="118"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="118"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2316,1903 +2320,1903 @@
   <dimension ref="A1:I67"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="44"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+    <row r="1" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="F2" s="8" t="n">
         <v>577</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A2)+COUNTIF(Faults!$M$2:$M$37,A2)</f>
         <v>1</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="9"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="I2" s="10"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="8" t="n">
         <v>730</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A3)+COUNTIF(Faults!$M$2:$M$37,A3)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="9"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="I3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="8" t="n">
         <v>485</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A4)+COUNTIF(Faults!$M$2:$M$37,A4)</f>
         <v>1</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="8" t="n">
         <v>376</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A5)+COUNTIF(Faults!$M$2:$M$37,A5)</f>
         <v>1</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="9"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <v>242</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A6)+COUNTIF(Faults!$M$2:$M$37,A6)</f>
         <v>1</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <v>292</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A7)+COUNTIF(Faults!$M$2:$M$37,A7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>990</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A8)+COUNTIF(Faults!$M$2:$M$37,A8)</f>
         <v>1</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="8" t="n">
         <v>795</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A9)+COUNTIF(Faults!$M$2:$M$37,A9)</f>
         <v>1</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="I9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="8" t="n">
         <v>107</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A10)+COUNTIF(Faults!$M$2:$M$37,A10)</f>
         <v>1</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="I10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="8" t="n">
         <v>449</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A11)+COUNTIF(Faults!$M$2:$M$37,A11)</f>
         <v>1</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="8" t="n">
         <v>617</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A12)+COUNTIF(Faults!$M$2:$M$37,A12)</f>
         <v>1</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="I12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="8" t="n">
         <v>999</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A13)+COUNTIF(Faults!$M$2:$M$37,A13)</f>
         <v>1</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="8" t="n">
         <v>722</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A14)+COUNTIF(Faults!$M$2:$M$37,A14)</f>
         <v>1</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="I14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="8" t="n">
         <v>183</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A15)+COUNTIF(Faults!$M$2:$M$37,A15)</f>
         <v>1</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="I15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="8" t="n">
         <v>445</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A16)+COUNTIF(Faults!$M$2:$M$37,A16)</f>
         <v>1</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="I16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="8" t="n">
         <v>670</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A17)+COUNTIF(Faults!$M$2:$M$37,A17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I17" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="I17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="8" t="n">
         <v>734</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A18)+COUNTIF(Faults!$M$2:$M$37,A18)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="9"/>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
+      <c r="I18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <v>340</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="11" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A19)+COUNTIF(Faults!$M$2:$M$37,A19)</f>
         <v>1</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="I19" s="14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="8" t="n">
         <v>819</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A20)+COUNTIF(Faults!$M$2:$M$37,A20)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I20" s="9"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="I20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="8" t="n">
         <v>142</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A21)+COUNTIF(Faults!$M$2:$M$37,A21)</f>
         <v>1</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="I21" s="9"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="I21" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="8" t="n">
         <v>848</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A22)+COUNTIF(Faults!$M$2:$M$37,A22)</f>
         <v>1</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="I22" s="9"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="I22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="8" t="n">
         <v>491</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A23)+COUNTIF(Faults!$M$2:$M$37,A23)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I23" s="9"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="I23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="8" t="n">
         <v>274</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A24)+COUNTIF(Faults!$M$2:$M$37,A24)</f>
         <v>1</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="I24" s="9"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="I24" s="10"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="F25" s="8" t="n">
         <v>823</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A25)+COUNTIF(Faults!$M$2:$M$37,A25)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I25" s="9"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="I25" s="10"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="8" t="n">
         <v>565</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A26)+COUNTIF(Faults!$M$2:$M$37,A26)</f>
         <v>1</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="I26" s="9"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="I26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F27" s="8" t="n">
         <v>845</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A27)+COUNTIF(Faults!$M$2:$M$37,A27)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I27" s="9"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="I27" s="10"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F28" s="8" t="n">
         <v>535</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A28)+COUNTIF(Faults!$M$2:$M$37,A28)</f>
         <v>1</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="I28" s="10"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="8" t="n">
         <v>261</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A29)+COUNTIF(Faults!$M$2:$M$37,A29)</f>
         <v>1</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+      <c r="I29" s="10"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="8" t="n">
         <v>273</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A30)+COUNTIF(Faults!$M$2:$M$37,A30)</f>
         <v>1</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+      <c r="I30" s="10"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F31" s="8" t="n">
         <v>346</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A31)+COUNTIF(Faults!$M$2:$M$37,A31)</f>
         <v>0</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="I31" s="10"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="8" t="n">
         <v>153</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A32)+COUNTIF(Faults!$M$2:$M$37,A32)</f>
         <v>1</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="I32" s="10"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F33" s="8" t="n">
         <v>214</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A33)+COUNTIF(Faults!$M$2:$M$37,A33)</f>
         <v>1</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="H33" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+      <c r="I33" s="10"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="8" t="n">
         <v>236</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A34)+COUNTIF(Faults!$M$2:$M$37,A34)</f>
         <v>0</v>
       </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="I34" s="10"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="8" t="n">
         <v>621</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A35)+COUNTIF(Faults!$M$2:$M$37,A35)</f>
         <v>1</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="I35" s="9"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+      <c r="I35" s="10"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="8" t="n">
         <v>707</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A36)+COUNTIF(Faults!$M$2:$M$37,A36)</f>
         <v>1</v>
       </c>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+      <c r="I36" s="10"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F37" s="8" t="n">
         <v>165</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A37)+COUNTIF(Faults!$M$2:$M$37,A37)</f>
         <v>0</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+      <c r="I37" s="10"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F38" s="8" t="n">
         <v>895</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G38" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A38)+COUNTIF(Faults!$M$2:$M$37,A38)</f>
         <v>1</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="I38" s="9"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
+      <c r="I38" s="10"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F39" s="8" t="n">
         <v>807</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G39" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A39)+COUNTIF(Faults!$M$2:$M$37,A39)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="H39" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I39" s="9"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+      <c r="I39" s="10"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="8" t="n">
         <v>495</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="G40" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A40)+COUNTIF(Faults!$M$2:$M$37,A40)</f>
         <v>1</v>
       </c>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="I40" s="9"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
+      <c r="I40" s="10"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="F41" s="8" t="n">
         <v>911</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="G41" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A41)+COUNTIF(Faults!$M$2:$M$37,A41)</f>
         <v>0</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I41" s="9"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+      <c r="I41" s="10"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="F42" s="7" t="n">
+      <c r="F42" s="8" t="n">
         <v>867</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="G42" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A42)+COUNTIF(Faults!$M$2:$M$37,A42)</f>
         <v>1</v>
       </c>
-      <c r="H42" s="8" t="s">
+      <c r="H42" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="I42" s="9"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
+      <c r="I42" s="10"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F43" s="7" t="n">
+      <c r="F43" s="8" t="n">
         <v>205</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A43)+COUNTIF(Faults!$M$2:$M$37,A43)</f>
         <v>1</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="I43" s="9"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
+      <c r="I43" s="10"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="8" t="n">
         <v>401</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="G44" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A44)+COUNTIF(Faults!$M$2:$M$37,A44)</f>
         <v>0</v>
       </c>
-      <c r="H44" s="8" t="s">
+      <c r="H44" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I44" s="9"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
+      <c r="I44" s="10"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" s="8" t="n">
         <v>311</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="G45" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A45)+COUNTIF(Faults!$M$2:$M$37,A45)</f>
         <v>1</v>
       </c>
-      <c r="H45" s="8" t="s">
+      <c r="H45" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="I45" s="9"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+      <c r="I45" s="10"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F46" s="8" t="n">
         <v>793</v>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G46" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A46)+COUNTIF(Faults!$M$2:$M$37,A46)</f>
         <v>1</v>
       </c>
-      <c r="H46" s="8" t="s">
+      <c r="H46" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="I46" s="9"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
+      <c r="I46" s="10"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="8" t="n">
         <v>331</v>
       </c>
-      <c r="G47" s="6" t="n">
+      <c r="G47" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A47)+COUNTIF(Faults!$M$2:$M$37,A47)</f>
         <v>0</v>
       </c>
-      <c r="H47" s="8" t="s">
+      <c r="H47" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I47" s="9"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="s">
+      <c r="I47" s="10"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="F48" s="7" t="n">
+      <c r="F48" s="8" t="n">
         <v>846</v>
       </c>
-      <c r="G48" s="6" t="n">
+      <c r="G48" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A48)+COUNTIF(Faults!$M$2:$M$37,A48)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="8" t="s">
+      <c r="H48" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I48" s="9"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
+      <c r="I48" s="10"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="F49" s="8" t="n">
         <v>915</v>
       </c>
-      <c r="G49" s="6" t="n">
+      <c r="G49" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A49)+COUNTIF(Faults!$M$2:$M$37,A49)</f>
         <v>1</v>
       </c>
-      <c r="H49" s="8" t="s">
+      <c r="H49" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="I49" s="9"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
+      <c r="I49" s="10"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F50" s="8" t="n">
         <v>534</v>
       </c>
-      <c r="G50" s="6" t="n">
+      <c r="G50" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A50)+COUNTIF(Faults!$M$2:$M$37,A50)</f>
         <v>1</v>
       </c>
-      <c r="H50" s="8" t="s">
+      <c r="H50" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="I50" s="9"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
+      <c r="I50" s="10"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="F51" s="7" t="n">
+      <c r="F51" s="8" t="n">
         <v>190</v>
       </c>
-      <c r="G51" s="6" t="n">
+      <c r="G51" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A51)+COUNTIF(Faults!$M$2:$M$37,A51)</f>
         <v>0</v>
       </c>
-      <c r="H51" s="8" t="s">
+      <c r="H51" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I51" s="9"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
+      <c r="I51" s="10"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="F52" s="7" t="n">
+      <c r="F52" s="8" t="n">
         <v>894</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G52" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A52)+COUNTIF(Faults!$M$2:$M$37,A52)</f>
         <v>1</v>
       </c>
-      <c r="H52" s="8" t="s">
+      <c r="H52" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="I52" s="9"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
+      <c r="I52" s="10"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F53" s="8" t="n">
         <v>996</v>
       </c>
-      <c r="G53" s="6" t="n">
+      <c r="G53" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A53)+COUNTIF(Faults!$M$2:$M$37,A53)</f>
         <v>1</v>
       </c>
-      <c r="H53" s="8" t="s">
+      <c r="H53" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="I53" s="9"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+      <c r="I53" s="10"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="F54" s="7" t="n">
+      <c r="F54" s="8" t="n">
         <v>316</v>
       </c>
-      <c r="G54" s="6" t="n">
+      <c r="G54" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A54)+COUNTIF(Faults!$M$2:$M$37,A54)</f>
         <v>0</v>
       </c>
-      <c r="H54" s="8" t="s">
+      <c r="H54" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I54" s="9"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+      <c r="I54" s="10"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="F55" s="7" t="n">
+      <c r="F55" s="8" t="n">
         <v>509</v>
       </c>
-      <c r="G55" s="6" t="n">
+      <c r="G55" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A55)+COUNTIF(Faults!$M$2:$M$37,A55)</f>
         <v>1</v>
       </c>
-      <c r="H55" s="8" t="s">
+      <c r="H55" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="I55" s="9"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
+      <c r="I55" s="10"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="E56" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="F56" s="7" t="n">
+      <c r="F56" s="8" t="n">
         <v>390</v>
       </c>
-      <c r="G56" s="6" t="n">
+      <c r="G56" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A56)+COUNTIF(Faults!$M$2:$M$37,A56)</f>
         <v>1</v>
       </c>
-      <c r="H56" s="8" t="s">
+      <c r="H56" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="I56" s="9"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
+      <c r="I56" s="10"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E57" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="F57" s="7" t="n">
+      <c r="F57" s="8" t="n">
         <v>452</v>
       </c>
-      <c r="G57" s="6" t="n">
+      <c r="G57" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A57)+COUNTIF(Faults!$M$2:$M$37,A57)</f>
         <v>0</v>
       </c>
-      <c r="H57" s="8" t="s">
+      <c r="H57" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I57" s="9"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="s">
+      <c r="I57" s="10"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E58" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="F58" s="7" t="n">
+      <c r="F58" s="8" t="n">
         <v>931</v>
       </c>
-      <c r="G58" s="6" t="n">
+      <c r="G58" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A58)+COUNTIF(Faults!$M$2:$M$37,A58)</f>
         <v>1</v>
       </c>
-      <c r="H58" s="8" t="s">
+      <c r="H58" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="I58" s="9"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
+      <c r="I58" s="10"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="F59" s="7" t="n">
+      <c r="F59" s="8" t="n">
         <v>145</v>
       </c>
-      <c r="G59" s="6" t="n">
+      <c r="G59" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A59)+COUNTIF(Faults!$M$2:$M$37,A59)</f>
         <v>0</v>
       </c>
-      <c r="H59" s="8" t="s">
+      <c r="H59" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I59" s="9"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="s">
+      <c r="I59" s="10"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D60" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="E60" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="F60" s="7" t="n">
+      <c r="F60" s="8" t="n">
         <v>306</v>
       </c>
-      <c r="G60" s="6" t="n">
+      <c r="G60" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A60)+COUNTIF(Faults!$M$2:$M$37,A60)</f>
         <v>1</v>
       </c>
-      <c r="H60" s="8" t="s">
+      <c r="H60" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="I60" s="9"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="s">
+      <c r="I60" s="10"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D61" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E61" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="F61" s="7" t="n">
+      <c r="F61" s="8" t="n">
         <v>828</v>
       </c>
-      <c r="G61" s="6" t="n">
+      <c r="G61" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A61)+COUNTIF(Faults!$M$2:$M$37,A61)</f>
         <v>0</v>
       </c>
-      <c r="H61" s="8" t="s">
+      <c r="H61" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I61" s="9"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="10" t="s">
+      <c r="I61" s="10"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D62" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="E62" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="F62" s="11" t="n">
+      <c r="F62" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="G62" s="10" t="n">
+      <c r="G62" s="11" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A62)+COUNTIF(Faults!$M$2:$M$37,A62)</f>
         <v>1</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="H62" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="I62" s="13" t="s">
+      <c r="I62" s="14" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="10" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B63" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C63" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D63" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="E63" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="F63" s="11" t="n">
+      <c r="F63" s="12" t="n">
         <v>524</v>
       </c>
-      <c r="G63" s="10" t="n">
+      <c r="G63" s="11" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A63)+COUNTIF(Faults!$M$2:$M$37,A63)</f>
         <v>1</v>
       </c>
-      <c r="H63" s="12" t="s">
+      <c r="H63" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="I63" s="13" t="s">
+      <c r="I63" s="14" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="10" t="s">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="C64" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D64" s="10" t="s">
+      <c r="D64" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E64" s="10" t="s">
+      <c r="E64" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="F64" s="11" t="n">
+      <c r="F64" s="12" t="n">
         <v>157</v>
       </c>
-      <c r="G64" s="10" t="n">
+      <c r="G64" s="11" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A64)+COUNTIF(Faults!$M$2:$M$37,A64)</f>
         <v>1</v>
       </c>
-      <c r="H64" s="12" t="s">
+      <c r="H64" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="I64" s="13" t="s">
+      <c r="I64" s="14" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="10" t="s">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="C65" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="D65" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="E65" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="F65" s="11" t="n">
+      <c r="F65" s="12" t="n">
         <v>490</v>
       </c>
-      <c r="G65" s="10" t="n">
+      <c r="G65" s="11" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A65)+COUNTIF(Faults!$M$2:$M$37,A65)</f>
         <v>1</v>
       </c>
-      <c r="H65" s="12" t="s">
+      <c r="H65" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="I65" s="13" t="s">
+      <c r="I65" s="14" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="10" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="C66" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="D66" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E66" s="10" t="s">
+      <c r="E66" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F66" s="11" t="n">
+      <c r="F66" s="12" t="n">
         <v>606</v>
       </c>
-      <c r="G66" s="10" t="n">
+      <c r="G66" s="11" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A66)+COUNTIF(Faults!$M$2:$M$37,A66)</f>
         <v>1</v>
       </c>
-      <c r="H66" s="12" t="s">
+      <c r="H66" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="I66" s="13" t="s">
+      <c r="I66" s="14" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="10" t="s">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C67" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="D67" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="E67" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="F67" s="11" t="n">
+      <c r="F67" s="12" t="n">
         <v>243</v>
       </c>
-      <c r="G67" s="10" t="n">
+      <c r="G67" s="11" t="n">
         <f aca="false">COUNTIF(Faults!$K$2:$K$37,A67)+COUNTIF(Faults!$M$2:$M$37,A67)</f>
         <v>1</v>
       </c>
-      <c r="H67" s="12" t="s">
+      <c r="H67" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="I67" s="13" t="s">
+      <c r="I67" s="14" t="s">
         <v>220</v>
       </c>
     </row>
@@ -4237,2027 +4241,2027 @@
   <dimension ref="A1:Q37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+    <row r="1" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="6" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="F2" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="14" t="n">
+      <c r="F2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="14" t="s">
+      <c r="H2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="16" t="n">
+      <c r="L2" s="17" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K2,SpecTables!$A:$A,0))</f>
         <v>577</v>
       </c>
-      <c r="M2" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="O2" s="18" t="str">
+      <c r="M2" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="O2" s="19" t="str">
         <f aca="false">J2&amp;"-"&amp;TEXT(L2,"000")</f>
         <v>P-01-577</v>
       </c>
-      <c r="P2" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q2" s="15" t="s">
+      <c r="P2" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q2" s="16" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="F3" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="14" t="n">
+      <c r="F3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="14" t="s">
+      <c r="H3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="L3" s="16" t="n">
+      <c r="L3" s="17" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K3,SpecTables!$A:$A,0))</f>
         <v>617</v>
       </c>
-      <c r="M3" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="N3" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="O3" s="18" t="str">
+      <c r="M3" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="N3" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="O3" s="19" t="str">
         <f aca="false">J3&amp;"-"&amp;TEXT(L3,"000")</f>
         <v>P-01-617</v>
       </c>
-      <c r="P3" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q3" s="15" t="s">
+      <c r="P3" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="14" t="s">
+      <c r="H4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="L4" s="16" t="n">
+      <c r="L4" s="17" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K4,SpecTables!$A:$A,0))</f>
         <v>848</v>
       </c>
-      <c r="M4" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="N4" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="O4" s="18" t="str">
+      <c r="M4" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="N4" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="O4" s="19" t="str">
         <f aca="false">J4&amp;"-"&amp;TEXT(L4,"000")</f>
         <v>P-01-848</v>
       </c>
-      <c r="P4" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q4" s="15" t="s">
+      <c r="P4" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q4" s="16" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="14" t="s">
+      <c r="H5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="L5" s="16" t="n">
+      <c r="L5" s="17" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K5,SpecTables!$A:$A,0))</f>
         <v>153</v>
       </c>
-      <c r="M5" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="N5" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="O5" s="18" t="str">
+      <c r="M5" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="N5" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="O5" s="19" t="str">
         <f aca="false">J5&amp;"-"&amp;TEXT(L5,"000")</f>
         <v>P-01-153</v>
       </c>
-      <c r="P5" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q5" s="15" t="s">
+      <c r="P5" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q5" s="16" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="14" t="n">
+      <c r="F6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="14" t="s">
+      <c r="H6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="L6" s="16" t="n">
+      <c r="L6" s="17" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K6,SpecTables!$A:$A,0))</f>
         <v>867</v>
       </c>
-      <c r="M6" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="N6" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="O6" s="18" t="str">
+      <c r="M6" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="N6" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="O6" s="19" t="str">
         <f aca="false">J6&amp;"-"&amp;TEXT(L6,"000")</f>
         <v>P-01-867</v>
       </c>
-      <c r="P6" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q6" s="15" t="s">
+      <c r="P6" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q6" s="16" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="F7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="14" t="n">
+      <c r="F7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="14" t="s">
+      <c r="H7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="L7" s="16" t="n">
+      <c r="L7" s="17" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K7,SpecTables!$A:$A,0))</f>
         <v>894</v>
       </c>
-      <c r="M7" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="O7" s="18" t="str">
+      <c r="M7" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="N7" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="O7" s="19" t="str">
         <f aca="false">J7&amp;"-"&amp;TEXT(L7,"000")</f>
         <v>P-01-894</v>
       </c>
-      <c r="P7" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q7" s="15" t="s">
+      <c r="P7" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q7" s="16" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="F8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="19" t="n">
+      <c r="F8" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="H8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="19" t="s">
+      <c r="H8" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="L8" s="21" t="n">
+      <c r="L8" s="22" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K8,SpecTables!$A:$A,0))</f>
         <v>990</v>
       </c>
-      <c r="M8" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="N8" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="O8" s="23" t="str">
+      <c r="M8" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="N8" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="O8" s="24" t="str">
         <f aca="false">J8&amp;"-"&amp;TEXT(L8,"000")</f>
         <v>P-02-990</v>
       </c>
-      <c r="P8" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q8" s="20"/>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="P8" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q8" s="21"/>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="F9" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="19" t="n">
+      <c r="F9" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="19" t="s">
+      <c r="I9" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="L9" s="21" t="n">
+      <c r="L9" s="22" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K9,SpecTables!$A:$A,0))</f>
         <v>485</v>
       </c>
-      <c r="M9" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="N9" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="O9" s="23" t="str">
+      <c r="M9" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="N9" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="O9" s="24" t="str">
         <f aca="false">J9&amp;"-"&amp;TEXT(L9,"000")</f>
         <v>P-03-485</v>
       </c>
-      <c r="P9" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q9" s="20"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="P9" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q9" s="21"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="F10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="19" t="n">
+      <c r="F10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="H10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="19" t="s">
+      <c r="H10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="L10" s="21" t="n">
+      <c r="L10" s="22" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K10,SpecTables!$A:$A,0))</f>
         <v>999</v>
       </c>
-      <c r="M10" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="N10" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="O10" s="23" t="str">
+      <c r="M10" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="N10" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="O10" s="24" t="str">
         <f aca="false">J10&amp;"-"&amp;TEXT(L10,"000")</f>
         <v>P-02-999</v>
       </c>
-      <c r="P10" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q10" s="20"/>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="P10" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q10" s="21"/>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="F11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="19" t="n">
+      <c r="F11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="J11" s="19" t="s">
+      <c r="J11" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="K11" s="19" t="s">
+      <c r="K11" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="L11" s="21" t="n">
+      <c r="L11" s="22" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K11,SpecTables!$A:$A,0))</f>
         <v>183</v>
       </c>
-      <c r="M11" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="N11" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="O11" s="23" t="str">
+      <c r="M11" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="N11" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="O11" s="24" t="str">
         <f aca="false">J11&amp;"-"&amp;TEXT(L11,"000")</f>
         <v>P-03-183</v>
       </c>
-      <c r="P11" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q11" s="20"/>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="P11" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q11" s="21"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="F12" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="19" t="s">
+      <c r="F12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="J12" s="19" t="s">
+      <c r="J12" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="K12" s="19" t="s">
+      <c r="K12" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="L12" s="21" t="n">
+      <c r="L12" s="22" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K12,SpecTables!$A:$A,0))</f>
         <v>535</v>
       </c>
-      <c r="M12" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="N12" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="O12" s="23" t="str">
+      <c r="M12" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="N12" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="O12" s="24" t="str">
         <f aca="false">J12&amp;"-"&amp;TEXT(L12,"000")</f>
         <v>P-02-535</v>
       </c>
-      <c r="P12" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q12" s="20"/>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="P12" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q12" s="21"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="F13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="19" t="n">
+      <c r="F13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="H13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="19" t="s">
+      <c r="H13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="J13" s="19" t="s">
+      <c r="J13" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="K13" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="L13" s="21" t="n">
+      <c r="L13" s="22" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K13,SpecTables!$A:$A,0))</f>
         <v>214</v>
       </c>
-      <c r="M13" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="N13" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="O13" s="23" t="str">
+      <c r="M13" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="N13" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="O13" s="24" t="str">
         <f aca="false">J13&amp;"-"&amp;TEXT(L13,"000")</f>
         <v>P-02-214</v>
       </c>
-      <c r="P13" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q13" s="20"/>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="P13" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q13" s="21"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="F14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="19" t="n">
+      <c r="F14" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="H14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="19" t="s">
+      <c r="H14" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="J14" s="19" t="s">
+      <c r="J14" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="K14" s="19" t="s">
+      <c r="K14" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="L14" s="21" t="n">
+      <c r="L14" s="22" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K14,SpecTables!$A:$A,0))</f>
         <v>205</v>
       </c>
-      <c r="M14" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="N14" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="O14" s="23" t="str">
+      <c r="M14" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="N14" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="O14" s="24" t="str">
         <f aca="false">J14&amp;"-"&amp;TEXT(L14,"000")</f>
         <v>P-02-205</v>
       </c>
-      <c r="P14" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q14" s="20"/>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+      <c r="P14" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q14" s="21"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="F15" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="19" t="n">
+      <c r="F15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="H15" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="19" t="s">
+      <c r="H15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="J15" s="19" t="s">
+      <c r="J15" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="K15" s="19" t="s">
+      <c r="K15" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="L15" s="21" t="n">
+      <c r="L15" s="22" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K15,SpecTables!$A:$A,0))</f>
         <v>996</v>
       </c>
-      <c r="M15" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="N15" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="O15" s="23" t="str">
+      <c r="M15" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="N15" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="O15" s="24" t="str">
         <f aca="false">J15&amp;"-"&amp;TEXT(L15,"000")</f>
         <v>P-02-996</v>
       </c>
-      <c r="P15" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q15" s="20"/>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
+      <c r="P15" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q15" s="21"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="25" t="s">
         <v>290</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="25" t="s">
         <v>291</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="F16" s="24" t="n">
+      <c r="F16" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="24" t="n">
+      <c r="G16" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="H16" s="24" t="n">
+      <c r="H16" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="24" t="s">
+      <c r="I16" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="J16" s="24" t="s">
+      <c r="J16" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="L16" s="25" t="n">
+      <c r="L16" s="26" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K16,SpecTables!$A:$A,0))</f>
         <v>340</v>
       </c>
-      <c r="M16" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="N16" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="O16" s="26" t="str">
+      <c r="M16" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="O16" s="27" t="str">
         <f aca="false">J16&amp;"-"&amp;TEXT(L16,"000")</f>
         <v>P-04-340</v>
       </c>
-      <c r="P16" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q16" s="13" t="s">
+      <c r="P16" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q16" s="14" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="s">
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="F17" s="27" t="n">
+      <c r="F17" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="27" t="n">
+      <c r="G17" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="27" t="s">
+      <c r="I17" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="J17" s="27" t="s">
+      <c r="J17" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K17" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="L17" s="29" t="n">
+      <c r="L17" s="30" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K17,SpecTables!$A:$A,0))</f>
         <v>445</v>
       </c>
-      <c r="M17" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="N17" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="O17" s="31" t="str">
+      <c r="M17" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="N17" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="O17" s="32" t="str">
         <f aca="false">J17&amp;"-"&amp;TEXT(L17,"000")</f>
         <v>P-05-445</v>
       </c>
-      <c r="P17" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q17" s="28"/>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="s">
+      <c r="P17" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q17" s="29"/>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="F18" s="27" t="n">
+      <c r="F18" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="G18" s="27" t="n">
+      <c r="G18" s="28" t="n">
         <v>1.5</v>
       </c>
-      <c r="H18" s="27" t="n">
+      <c r="H18" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="27" t="s">
+      <c r="I18" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="J18" s="27" t="s">
+      <c r="J18" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="K18" s="27" t="s">
+      <c r="K18" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="L18" s="29" t="n">
+      <c r="L18" s="30" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K18,SpecTables!$A:$A,0))</f>
         <v>274</v>
       </c>
-      <c r="M18" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="N18" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="O18" s="31" t="str">
+      <c r="M18" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="N18" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="O18" s="32" t="str">
         <f aca="false">J18&amp;"-"&amp;TEXT(L18,"000")</f>
         <v>P-04-274</v>
       </c>
-      <c r="P18" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q18" s="28"/>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="s">
+      <c r="P18" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q18" s="29"/>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="29" t="s">
         <v>303</v>
       </c>
-      <c r="F19" s="27" t="n">
+      <c r="F19" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="27" t="n">
+      <c r="G19" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="27" t="s">
+      <c r="I19" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="J19" s="27" t="s">
+      <c r="J19" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="K19" s="27" t="s">
+      <c r="K19" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="L19" s="29" t="n">
+      <c r="L19" s="30" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K19,SpecTables!$A:$A,0))</f>
         <v>273</v>
       </c>
-      <c r="M19" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="N19" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="O19" s="31" t="str">
+      <c r="M19" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="N19" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="O19" s="32" t="str">
         <f aca="false">J19&amp;"-"&amp;TEXT(L19,"000")</f>
         <v>P-05-273</v>
       </c>
-      <c r="P19" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q19" s="28"/>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27" t="s">
+      <c r="P19" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q19" s="29"/>
+    </row>
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="29" t="s">
         <v>306</v>
       </c>
-      <c r="F20" s="27" t="n">
+      <c r="F20" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="27" t="n">
+      <c r="G20" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="H20" s="27" t="n">
+      <c r="H20" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="27" t="s">
+      <c r="I20" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="J20" s="27" t="s">
+      <c r="J20" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="K20" s="27" t="s">
+      <c r="K20" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="L20" s="29" t="n">
+      <c r="L20" s="30" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K20,SpecTables!$A:$A,0))</f>
         <v>621</v>
       </c>
-      <c r="M20" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="N20" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="O20" s="31" t="str">
+      <c r="M20" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="N20" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="O20" s="32" t="str">
         <f aca="false">J20&amp;"-"&amp;TEXT(L20,"000")</f>
         <v>P-04-621</v>
       </c>
-      <c r="P20" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q20" s="28"/>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27" t="s">
+      <c r="P20" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q20" s="29"/>
+    </row>
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="F21" s="27" t="n">
+      <c r="F21" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="G21" s="27" t="n">
+      <c r="G21" s="28" t="n">
         <v>1.5</v>
       </c>
-      <c r="H21" s="27" t="n">
+      <c r="H21" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I21" s="27" t="s">
+      <c r="I21" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="J21" s="27" t="s">
+      <c r="J21" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="K21" s="27" t="s">
+      <c r="K21" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="L21" s="29" t="n">
+      <c r="L21" s="30" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K21,SpecTables!$A:$A,0))</f>
         <v>895</v>
       </c>
-      <c r="M21" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="N21" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="O21" s="31" t="str">
+      <c r="M21" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="N21" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="O21" s="32" t="str">
         <f aca="false">J21&amp;"-"&amp;TEXT(L21,"000")</f>
         <v>P-05-895</v>
       </c>
-      <c r="P21" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q21" s="28"/>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="27" t="s">
+      <c r="P21" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q21" s="29"/>
+    </row>
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="E22" s="29" t="s">
         <v>311</v>
       </c>
-      <c r="F22" s="27" t="n">
+      <c r="F22" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="27" t="n">
+      <c r="G22" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="27" t="n">
+      <c r="H22" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="27" t="s">
+      <c r="I22" s="28" t="s">
         <v>293</v>
       </c>
-      <c r="J22" s="27" t="s">
+      <c r="J22" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="K22" s="27" t="s">
+      <c r="K22" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="L22" s="29" t="n">
+      <c r="L22" s="30" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K22,SpecTables!$A:$A,0))</f>
         <v>311</v>
       </c>
-      <c r="M22" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="N22" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="O22" s="31" t="str">
+      <c r="M22" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="N22" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="O22" s="32" t="str">
         <f aca="false">J22&amp;"-"&amp;TEXT(L22,"000")</f>
         <v>P-04-311</v>
       </c>
-      <c r="P22" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q22" s="28" t="s">
+      <c r="P22" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q22" s="29" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="s">
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="28" t="s">
         <v>313</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="29" t="s">
         <v>314</v>
       </c>
-      <c r="F23" s="27" t="n">
+      <c r="F23" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="27" t="n">
+      <c r="G23" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="27" t="s">
+      <c r="I23" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="J23" s="27" t="s">
+      <c r="J23" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="K23" s="27" t="s">
+      <c r="K23" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="L23" s="29" t="n">
+      <c r="L23" s="30" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K23,SpecTables!$A:$A,0))</f>
         <v>915</v>
       </c>
-      <c r="M23" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="N23" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="O23" s="31" t="str">
+      <c r="M23" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="N23" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="O23" s="32" t="str">
         <f aca="false">J23&amp;"-"&amp;TEXT(L23,"000")</f>
         <v>P-05-915</v>
       </c>
-      <c r="P23" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q23" s="28"/>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="27" t="s">
+      <c r="P23" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q23" s="29"/>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="28" t="s">
         <v>315</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F24" s="27" t="n">
+      <c r="F24" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="G24" s="28" t="n">
         <v>1.5</v>
       </c>
-      <c r="H24" s="27" t="n">
+      <c r="H24" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="27" t="s">
+      <c r="I24" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="J24" s="27" t="s">
+      <c r="J24" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="K24" s="27" t="s">
+      <c r="K24" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="L24" s="29" t="n">
+      <c r="L24" s="30" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K24,SpecTables!$A:$A,0))</f>
         <v>931</v>
       </c>
-      <c r="M24" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="N24" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="O24" s="31" t="str">
+      <c r="M24" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="N24" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="O24" s="32" t="str">
         <f aca="false">J24&amp;"-"&amp;TEXT(L24,"000")</f>
         <v>P-04-931</v>
       </c>
-      <c r="P24" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q24" s="28"/>
-    </row>
-    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24" t="s">
+      <c r="P24" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q24" s="29"/>
+    </row>
+    <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="25" t="s">
         <v>317</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="25" t="s">
         <v>290</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="25" t="s">
         <v>318</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="24" t="n">
+      <c r="G25" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="24" t="n">
+      <c r="H25" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="J25" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="K25" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="O25" s="26" t="s">
+      <c r="I25" s="25" t="s">
+        <v>253</v>
+      </c>
+      <c r="J25" s="25" t="s">
+        <v>253</v>
+      </c>
+      <c r="K25" s="25" t="s">
+        <v>253</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="O25" s="27" t="s">
         <v>320</v>
       </c>
-      <c r="P25" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q25" s="13" t="s">
+      <c r="P25" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q25" s="14" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="27" t="s">
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="28" t="s">
         <v>322</v>
       </c>
-      <c r="E26" s="28" t="s">
+      <c r="E26" s="29" t="s">
         <v>323</v>
       </c>
-      <c r="F26" s="27" t="n">
+      <c r="F26" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="27" t="n">
+      <c r="G26" s="28" t="n">
         <v>1.5</v>
       </c>
-      <c r="H26" s="27" t="n">
+      <c r="H26" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="27" t="s">
+      <c r="I26" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="J26" s="27" t="s">
+      <c r="J26" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="K26" s="27" t="s">
+      <c r="K26" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="L26" s="29" t="n">
+      <c r="L26" s="30" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K26,SpecTables!$A:$A,0))</f>
         <v>107</v>
       </c>
-      <c r="M26" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="N26" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="O26" s="31" t="str">
+      <c r="M26" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="N26" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="O26" s="32" t="str">
         <f aca="false">J26&amp;"-"&amp;TEXT(L26,"000")</f>
         <v>P-04-107</v>
       </c>
-      <c r="P26" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q26" s="28"/>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="27" t="s">
+      <c r="P26" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q26" s="29"/>
+    </row>
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="D27" s="28" t="s">
         <v>324</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="29" t="s">
         <v>325</v>
       </c>
-      <c r="F27" s="27" t="n">
+      <c r="F27" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="27" t="n">
+      <c r="G27" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="27" t="s">
+      <c r="I27" s="28" t="s">
         <v>267</v>
       </c>
-      <c r="J27" s="27" t="s">
+      <c r="J27" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="K27" s="27" t="s">
+      <c r="K27" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="L27" s="29" t="n">
+      <c r="L27" s="30" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K27,SpecTables!$A:$A,0))</f>
         <v>376</v>
       </c>
-      <c r="M27" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="N27" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="O27" s="31" t="str">
+      <c r="M27" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="N27" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="O27" s="32" t="str">
         <f aca="false">J27&amp;"-"&amp;TEXT(L27,"000")</f>
         <v>P-05-376</v>
       </c>
-      <c r="P27" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q27" s="28"/>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="32" t="s">
+      <c r="P27" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q27" s="29"/>
+    </row>
+    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="33" t="s">
         <v>327</v>
       </c>
-      <c r="E28" s="33" t="s">
+      <c r="E28" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="F28" s="32" t="n">
+      <c r="F28" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G28" s="32" t="n">
+      <c r="G28" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="H28" s="32" t="n">
+      <c r="H28" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I28" s="32" t="s">
+      <c r="I28" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="J28" s="32" t="s">
+      <c r="J28" s="33" t="s">
         <v>330</v>
       </c>
-      <c r="K28" s="32" t="s">
+      <c r="K28" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="L28" s="34" t="n">
+      <c r="L28" s="35" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K28,SpecTables!$A:$A,0))</f>
         <v>142</v>
       </c>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="N28" s="34" t="n">
+      <c r="N28" s="35" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(M28,SpecTables!$A:$A,0))</f>
         <v>261</v>
       </c>
-      <c r="O28" s="36" t="str">
+      <c r="O28" s="37" t="str">
         <f aca="false">J28&amp;"-"&amp;TEXT(L28,"000")&amp;"-"&amp;TEXT(N28,"000")</f>
         <v>P-06-142-261</v>
       </c>
-      <c r="P28" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q28" s="33"/>
-    </row>
-    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="32" t="s">
+      <c r="P28" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q28" s="34"/>
+    </row>
+    <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="C29" s="32" t="s">
+      <c r="C29" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="33" t="s">
         <v>331</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="E29" s="34" t="s">
         <v>332</v>
       </c>
-      <c r="F29" s="32" t="n">
+      <c r="F29" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="32" t="n">
+      <c r="G29" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="32" t="n">
+      <c r="H29" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I29" s="32" t="s">
+      <c r="I29" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="J29" s="32" t="s">
+      <c r="J29" s="33" t="s">
         <v>330</v>
       </c>
-      <c r="K29" s="32" t="s">
+      <c r="K29" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="L29" s="34" t="n">
+      <c r="L29" s="35" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K29,SpecTables!$A:$A,0))</f>
         <v>565</v>
       </c>
-      <c r="M29" s="35" t="s">
+      <c r="M29" s="36" t="s">
         <v>221</v>
       </c>
-      <c r="N29" s="34" t="n">
+      <c r="N29" s="35" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(M29,SpecTables!$A:$A,0))</f>
         <v>524</v>
       </c>
-      <c r="O29" s="36" t="str">
+      <c r="O29" s="37" t="str">
         <f aca="false">J29&amp;"-"&amp;TEXT(L29,"000")&amp;"-"&amp;TEXT(N29,"000")</f>
         <v>P-06-565-524</v>
       </c>
-      <c r="P29" s="35" t="s">
+      <c r="P29" s="36" t="s">
         <v>334</v>
       </c>
-      <c r="Q29" s="33" t="s">
+      <c r="Q29" s="34" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32" t="s">
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="33" t="s">
         <v>336</v>
       </c>
-      <c r="E30" s="33" t="s">
+      <c r="E30" s="34" t="s">
         <v>337</v>
       </c>
-      <c r="F30" s="32" t="n">
+      <c r="F30" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="32" t="n">
+      <c r="G30" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="H30" s="32" t="n">
+      <c r="H30" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I30" s="32" t="s">
+      <c r="I30" s="33" t="s">
         <v>338</v>
       </c>
-      <c r="J30" s="32" t="s">
+      <c r="J30" s="33" t="s">
         <v>330</v>
       </c>
-      <c r="K30" s="32" t="s">
+      <c r="K30" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="L30" s="34" t="n">
+      <c r="L30" s="35" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K30,SpecTables!$A:$A,0))</f>
         <v>707</v>
       </c>
-      <c r="M30" s="35" t="s">
+      <c r="M30" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="N30" s="34" t="n">
+      <c r="N30" s="35" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(M30,SpecTables!$A:$A,0))</f>
         <v>449</v>
       </c>
-      <c r="O30" s="36" t="str">
+      <c r="O30" s="37" t="str">
         <f aca="false">J30&amp;"-"&amp;TEXT(L30,"000")&amp;"-"&amp;TEXT(N30,"000")</f>
         <v>P-06-707-449</v>
       </c>
-      <c r="P30" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q30" s="33" t="s">
+      <c r="P30" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q30" s="34" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="32" t="s">
+    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="33" t="s">
         <v>340</v>
       </c>
-      <c r="E31" s="33" t="s">
+      <c r="E31" s="34" t="s">
         <v>341</v>
       </c>
-      <c r="F31" s="32" t="n">
+      <c r="F31" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="32" t="n">
+      <c r="G31" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="H31" s="32" t="n">
+      <c r="H31" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="32" t="s">
+      <c r="I31" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="J31" s="32" t="s">
+      <c r="J31" s="33" t="s">
         <v>330</v>
       </c>
-      <c r="K31" s="32" t="s">
+      <c r="K31" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="L31" s="34" t="n">
+      <c r="L31" s="35" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K31,SpecTables!$A:$A,0))</f>
         <v>793</v>
       </c>
-      <c r="M31" s="35" t="s">
+      <c r="M31" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="N31" s="34" t="n">
+      <c r="N31" s="35" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(M31,SpecTables!$A:$A,0))</f>
         <v>509</v>
       </c>
-      <c r="O31" s="36" t="str">
+      <c r="O31" s="37" t="str">
         <f aca="false">J31&amp;"-"&amp;TEXT(L31,"000")&amp;"-"&amp;TEXT(N31,"000")</f>
         <v>P-06-793-509</v>
       </c>
-      <c r="P31" s="35" t="s">
+      <c r="P31" s="36" t="s">
         <v>342</v>
       </c>
-      <c r="Q31" s="33" t="s">
+      <c r="Q31" s="34" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="32" t="s">
+    <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="33" t="s">
         <v>344</v>
       </c>
-      <c r="E32" s="33" t="s">
+      <c r="E32" s="34" t="s">
         <v>345</v>
       </c>
-      <c r="F32" s="32" t="n">
+      <c r="F32" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G32" s="32" t="n">
+      <c r="G32" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="H32" s="32" t="n">
+      <c r="H32" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I32" s="32" t="s">
+      <c r="I32" s="33" t="s">
         <v>346</v>
       </c>
-      <c r="J32" s="32" t="s">
+      <c r="J32" s="33" t="s">
         <v>330</v>
       </c>
-      <c r="K32" s="32" t="s">
+      <c r="K32" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="L32" s="34" t="n">
+      <c r="L32" s="35" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K32,SpecTables!$A:$A,0))</f>
         <v>306</v>
       </c>
-      <c r="M32" s="35" t="s">
+      <c r="M32" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="N32" s="34" t="n">
+      <c r="N32" s="35" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(M32,SpecTables!$A:$A,0))</f>
         <v>606</v>
       </c>
-      <c r="O32" s="36" t="str">
+      <c r="O32" s="37" t="str">
         <f aca="false">J32&amp;"-"&amp;TEXT(L32,"000")&amp;"-"&amp;TEXT(N32,"000")</f>
         <v>P-06-306-606</v>
       </c>
-      <c r="P32" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q32" s="33" t="s">
+      <c r="P32" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q32" s="34" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="32" t="s">
+    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="32" t="s">
+      <c r="B33" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="C33" s="32" t="s">
+      <c r="C33" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="33" t="s">
         <v>348</v>
       </c>
-      <c r="E33" s="33" t="s">
+      <c r="E33" s="34" t="s">
         <v>349</v>
       </c>
-      <c r="F33" s="32" t="n">
+      <c r="F33" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G33" s="32" t="n">
+      <c r="G33" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="H33" s="32" t="n">
+      <c r="H33" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I33" s="32" t="s">
+      <c r="I33" s="33" t="s">
         <v>350</v>
       </c>
-      <c r="J33" s="32" t="s">
+      <c r="J33" s="33" t="s">
         <v>330</v>
       </c>
-      <c r="K33" s="32" t="s">
+      <c r="K33" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="L33" s="34" t="n">
+      <c r="L33" s="35" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K33,SpecTables!$A:$A,0))</f>
         <v>242</v>
       </c>
-      <c r="M33" s="35" t="s">
+      <c r="M33" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="N33" s="34" t="n">
+      <c r="N33" s="35" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(M33,SpecTables!$A:$A,0))</f>
         <v>495</v>
       </c>
-      <c r="O33" s="36" t="str">
+      <c r="O33" s="37" t="str">
         <f aca="false">J33&amp;"-"&amp;TEXT(L33,"000")&amp;"-"&amp;TEXT(N33,"000")</f>
         <v>P-06-242-495</v>
       </c>
-      <c r="P33" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q33" s="33" t="s">
+      <c r="P33" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q33" s="34" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="37" t="s">
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="B34" s="37" t="s">
+      <c r="B34" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="C34" s="37" t="s">
+      <c r="C34" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="D34" s="37" t="s">
+      <c r="D34" s="38" t="s">
         <v>353</v>
       </c>
-      <c r="E34" s="38" t="s">
+      <c r="E34" s="39" t="s">
         <v>354</v>
       </c>
-      <c r="F34" s="37" t="n">
+      <c r="F34" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="G34" s="37" t="n">
+      <c r="G34" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="37" t="n">
+      <c r="H34" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="I34" s="37" t="s">
+      <c r="I34" s="38" t="s">
         <v>350</v>
       </c>
-      <c r="J34" s="37" t="s">
+      <c r="J34" s="38" t="s">
         <v>355</v>
       </c>
-      <c r="K34" s="37" t="s">
+      <c r="K34" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="L34" s="39" t="n">
+      <c r="L34" s="40" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K34,SpecTables!$A:$A,0))</f>
         <v>243</v>
       </c>
-      <c r="M34" s="40" t="s">
+      <c r="M34" s="41" t="s">
         <v>181</v>
       </c>
-      <c r="N34" s="39" t="n">
+      <c r="N34" s="40" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(M34,SpecTables!$A:$A,0))</f>
         <v>534</v>
       </c>
-      <c r="O34" s="41" t="str">
+      <c r="O34" s="42" t="str">
         <f aca="false">J34&amp;"-"&amp;TEXT(L34,"000")&amp;"-"&amp;TEXT(N34,"000")</f>
         <v>P-07-243-534</v>
       </c>
-      <c r="P34" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q34" s="38" t="s">
+      <c r="P34" s="41" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q34" s="39" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="37" t="s">
+    <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="37" t="s">
+      <c r="B35" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="C35" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="37" t="s">
+      <c r="D35" s="38" t="s">
         <v>357</v>
       </c>
-      <c r="E35" s="38" t="s">
+      <c r="E35" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="F35" s="37" t="n">
+      <c r="F35" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="G35" s="37" t="n">
+      <c r="G35" s="38" t="n">
         <v>2.5</v>
       </c>
-      <c r="H35" s="37" t="n">
+      <c r="H35" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="I35" s="37" t="s">
+      <c r="I35" s="38" t="s">
         <v>359</v>
       </c>
-      <c r="J35" s="37" t="s">
+      <c r="J35" s="38" t="s">
         <v>355</v>
       </c>
-      <c r="K35" s="37" t="s">
+      <c r="K35" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="L35" s="39" t="n">
+      <c r="L35" s="40" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K35,SpecTables!$A:$A,0))</f>
         <v>106</v>
       </c>
-      <c r="M35" s="40" t="s">
+      <c r="M35" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="N35" s="39" t="n">
+      <c r="N35" s="40" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(M35,SpecTables!$A:$A,0))</f>
         <v>722</v>
       </c>
-      <c r="O35" s="41" t="str">
+      <c r="O35" s="42" t="str">
         <f aca="false">J35&amp;"-"&amp;TEXT(L35,"000")&amp;"-"&amp;TEXT(N35,"000")</f>
         <v>P-07-106-722</v>
       </c>
-      <c r="P35" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q35" s="38" t="s">
+      <c r="P35" s="41" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q35" s="39" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="37" t="s">
+    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="37" t="s">
+      <c r="B36" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="C36" s="37" t="s">
+      <c r="C36" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="37" t="s">
+      <c r="D36" s="38" t="s">
         <v>361</v>
       </c>
-      <c r="E36" s="38" t="s">
+      <c r="E36" s="39" t="s">
         <v>362</v>
       </c>
-      <c r="F36" s="37" t="n">
+      <c r="F36" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="G36" s="37" t="n">
+      <c r="G36" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="37" t="n">
+      <c r="H36" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="I36" s="37" t="s">
+      <c r="I36" s="38" t="s">
         <v>304</v>
       </c>
-      <c r="J36" s="37" t="s">
+      <c r="J36" s="38" t="s">
         <v>355</v>
       </c>
-      <c r="K36" s="37" t="s">
+      <c r="K36" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="L36" s="39" t="n">
+      <c r="L36" s="40" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K36,SpecTables!$A:$A,0))</f>
         <v>490</v>
       </c>
-      <c r="M36" s="40" t="s">
+      <c r="M36" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="N36" s="39" t="n">
+      <c r="N36" s="40" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(M36,SpecTables!$A:$A,0))</f>
         <v>795</v>
       </c>
-      <c r="O36" s="41" t="str">
+      <c r="O36" s="42" t="str">
         <f aca="false">J36&amp;"-"&amp;TEXT(L36,"000")&amp;"-"&amp;TEXT(N36,"000")</f>
         <v>P-07-490-795</v>
       </c>
-      <c r="P36" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q36" s="38" t="s">
+      <c r="P36" s="41" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q36" s="39" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="37" t="s">
+    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="B37" s="37" t="s">
+      <c r="B37" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C37" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="D37" s="37" t="s">
+      <c r="D37" s="38" t="s">
         <v>364</v>
       </c>
-      <c r="E37" s="38" t="s">
+      <c r="E37" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="F37" s="37" t="n">
+      <c r="F37" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="G37" s="37" t="n">
+      <c r="G37" s="38" t="n">
         <v>1.5</v>
       </c>
-      <c r="H37" s="37" t="n">
+      <c r="H37" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="37" t="s">
+      <c r="I37" s="38" t="s">
         <v>309</v>
       </c>
-      <c r="J37" s="37" t="s">
+      <c r="J37" s="38" t="s">
         <v>355</v>
       </c>
-      <c r="K37" s="37" t="s">
+      <c r="K37" s="38" t="s">
         <v>223</v>
       </c>
-      <c r="L37" s="39" t="n">
+      <c r="L37" s="40" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(K37,SpecTables!$A:$A,0))</f>
         <v>157</v>
       </c>
-      <c r="M37" s="40" t="s">
+      <c r="M37" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="N37" s="39" t="n">
+      <c r="N37" s="40" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH(M37,SpecTables!$A:$A,0))</f>
         <v>390</v>
       </c>
-      <c r="O37" s="41" t="str">
+      <c r="O37" s="42" t="str">
         <f aca="false">J37&amp;"-"&amp;TEXT(L37,"000")&amp;"-"&amp;TEXT(N37,"000")</f>
         <v>P-07-157-390</v>
       </c>
-      <c r="P37" s="40" t="s">
+      <c r="P37" s="41" t="s">
         <v>366</v>
       </c>
-      <c r="Q37" s="38" t="s">
+      <c r="Q37" s="39" t="s">
         <v>367</v>
       </c>
     </row>
@@ -6282,270 +6286,270 @@
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="42" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="43" t="s">
         <v>370</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="44" t="s">
         <v>371</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="44" t="s">
         <v>372</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="44" t="s">
         <v>373</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="44" t="s">
         <v>374</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="44" t="s">
         <v>375</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="44" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="45" t="s">
         <v>377</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="29" t="s">
         <v>379</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="29" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
+    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="45" t="s">
         <v>381</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="29" t="s">
         <v>383</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="10" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="s">
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="45" t="s">
         <v>384</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="29" t="s">
         <v>385</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="29" t="s">
         <v>387</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="10" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="s">
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="45" t="s">
         <v>388</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="29" t="s">
         <v>390</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="G8" s="29" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44" t="s">
+    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="45" t="s">
         <v>392</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="21" t="s">
         <v>393</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="G9" s="29" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="s">
+    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="45" t="s">
         <v>395</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="21" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="45" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="46" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="46" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="47" t="s">
         <v>400</v>
       </c>
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="48" t="s">
         <v>401</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="46" t="s">
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="47" t="s">
         <v>402</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="48" t="s">
         <v>403</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="46" t="s">
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="47" t="s">
         <v>404</v>
       </c>
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="48" t="s">
         <v>405</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="46" t="s">
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="47" t="s">
         <v>406</v>
       </c>
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="48" t="s">
         <v>407</v>
       </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="46" t="s">
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="47" t="s">
         <v>408</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="48" t="s">
         <v>409</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="46" t="s">
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="47" t="s">
         <v>410</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="48" t="s">
         <v>411</v>
       </c>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -6574,349 +6578,349 @@
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="110"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="44" t="s">
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="44" t="s">
+    <row r="3" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="44" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="s">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="s">
+    <row r="8" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44" t="s">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="s">
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="44" t="s">
+    <row r="13" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="44" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="10" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="44" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="10" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="44" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="10" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="44" t="s">
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="44" t="s">
+    <row r="18" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="44" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="10" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="44" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="10" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="44" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="10" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="44" t="s">
+    <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="10" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="44" t="s">
+    <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="10" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="44" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="10" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="44" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="10" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="44" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="10" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="44" t="s">
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="10" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="44" t="s">
+    <row r="28" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="10" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="44" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="10" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="44" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="10" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="44" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="10" t="s">
         <v>423</v>
       </c>
     </row>
@@ -6939,266 +6943,266 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$B$2:$B$37,"R0")</f>
         <v>6</v>
       </c>
-      <c r="D2" s="44" t="str">
+      <c r="D2" s="45" t="str">
         <f aca="false">IF(C2=6,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$B$2:$B$37,"R1")</f>
         <v>8</v>
       </c>
-      <c r="D3" s="44" t="str">
+      <c r="D3" s="45" t="str">
         <f aca="false">IF(C3=8,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$B$2:$B$37,"R2")</f>
         <v>12</v>
       </c>
-      <c r="D4" s="44" t="str">
+      <c r="D4" s="45" t="str">
         <f aca="false">IF(C4=12,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$B$2:$B$37,"R3")</f>
         <v>6</v>
       </c>
-      <c r="D5" s="44" t="str">
+      <c r="D5" s="45" t="str">
         <f aca="false">IF(C5=6,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <f aca="false">COUNTIF(Faults!$B$2:$B$37,"R4")</f>
         <v>4</v>
       </c>
-      <c r="D6" s="44" t="str">
+      <c r="D6" s="45" t="str">
         <f aca="false">IF(C6=4,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <f aca="false">SUMPRODUCT(COUNTIF(SpecTables!$F$2:$F$67,SpecTables!$F$2:$F$67))</f>
         <v>66</v>
       </c>
-      <c r="D7" s="44" t="str">
+      <c r="D7" s="45" t="str">
         <f aca="false">IF(C7=66,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <f aca="false">SUMPRODUCT((COUNTIF(Faults!$K$2:$K$37,{"PC-1";"WC-1";"MC-1";"TC-1";"AC-1";"CC-1"})+COUNTIF(Faults!$M$2:$M$37,{"PC-1";"WC-1";"MC-1";"TC-1";"AC-1";"CC-1"})&gt;0)*1)</f>
         <v>6</v>
       </c>
-      <c r="D8" s="44" t="str">
+      <c r="D8" s="45" t="str">
         <f aca="false">IF(C8=6,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>340</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <f aca="false">INDEX(SpecTables!$F:$F,MATCH("W4-3",SpecTables!$A:$A,0))</f>
         <v>340</v>
       </c>
-      <c r="D9" s="44" t="str">
+      <c r="D9" s="45" t="str">
         <f aca="false">IF(C9=340,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="7" t="n">
         <f aca="false">COUNTIF(SpecTables!$F$2:$F$67,290)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="44" t="str">
+      <c r="D10" s="45" t="str">
         <f aca="false">IF(C10=0,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <f aca="false">SUMIFS(SpecTables!$G$2:$G$67,SpecTables!$B$2:$B$67,"POW")</f>
         <v>9</v>
       </c>
-      <c r="D11" s="44" t="str">
+      <c r="D11" s="45" t="str">
         <f aca="false">IF(C11&gt;=2,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <f aca="false">SUMIFS(SpecTables!$G$2:$G$67,SpecTables!$B$2:$B$67,"WTR")</f>
         <v>8</v>
       </c>
-      <c r="D12" s="44" t="str">
+      <c r="D12" s="45" t="str">
         <f aca="false">IF(C12&gt;=2,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <f aca="false">SUMIFS(SpecTables!$G$2:$G$67,SpecTables!$B$2:$B$67,"MED")</f>
         <v>7</v>
       </c>
-      <c r="D13" s="44" t="str">
+      <c r="D13" s="45" t="str">
         <f aca="false">IF(C13&gt;=2,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <f aca="false">SUMIFS(SpecTables!$G$2:$G$67,SpecTables!$B$2:$B$67,"TRN")</f>
         <v>7</v>
       </c>
-      <c r="D14" s="44" t="str">
+      <c r="D14" s="45" t="str">
         <f aca="false">IF(C14&gt;=2,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="7" t="n">
         <f aca="false">SUMIFS(SpecTables!$G$2:$G$67,SpecTables!$B$2:$B$67,"AGR")</f>
         <v>7</v>
       </c>
-      <c r="D15" s="44" t="str">
+      <c r="D15" s="45" t="str">
         <f aca="false">IF(C15&gt;=2,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <f aca="false">SUMIFS(SpecTables!$G$2:$G$67,SpecTables!$B$2:$B$67,"COM")</f>
         <v>7</v>
       </c>
-      <c r="D16" s="44" t="str">
+      <c r="D16" s="45" t="str">
         <f aca="false">IF(C16&gt;=2,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>464</v>
       </c>
     </row>
